--- a/output/roomself_excel/7744.xlsx
+++ b/output/roomself_excel/7744.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>257768</v>
+        <v>28240</v>
       </c>
       <c r="D2" t="n">
-        <v>5272</v>
+        <v>1368</v>
       </c>
       <c r="E2" t="n">
-        <v>614</v>
+        <v>224</v>
       </c>
       <c r="F2" t="n">
-        <v>574</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3">
@@ -502,6 +502,50 @@
       </c>
       <c r="F3" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>42445</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1664</v>
+      </c>
+      <c r="E4" t="n">
+        <v>263</v>
+      </c>
+      <c r="F4" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>187083</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3552</v>
+      </c>
+      <c r="E5" t="n">
+        <v>614</v>
+      </c>
+      <c r="F5" t="n">
+        <v>574</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/7744.xlsx
+++ b/output/roomself_excel/7744.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,31 @@
       <c r="D2" t="n">
         <v>1368</v>
       </c>
-      <c r="E2" t="n">
-        <v>224</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>223</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="G2" t="n">
+        <v>55</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>168</v>
+      </c>
+      <c r="J2" t="n">
+        <v>50</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +551,23 @@
       <c r="D3" t="n">
         <v>1132</v>
       </c>
-      <c r="E3" t="n">
-        <v>355</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="G3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +584,31 @@
       <c r="D4" t="n">
         <v>1664</v>
       </c>
-      <c r="E4" t="n">
-        <v>263</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>204</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="G4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>233</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +625,38 @@
       <c r="D5" t="n">
         <v>3552</v>
       </c>
-      <c r="E5" t="n">
-        <v>614</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>574</v>
+        <v>390</v>
+      </c>
+      <c r="G5" t="n">
+        <v>55</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>498</v>
+      </c>
+      <c r="J5" t="n">
+        <v>51</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>351</v>
+      </c>
+      <c r="M5" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
